--- a/持仓模板20260703.xlsx
+++ b/持仓模板20260703.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rx_aitest\ai_trading\TradingAgents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74396127-EC35-4D37-8FC3-A291F57A7FB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AEDC2A-14CF-40D5-A076-85E4190B4EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,7 +453,7 @@
         <v>6100</v>
       </c>
       <c r="D3">
-        <v>15.91</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
@@ -461,13 +461,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>18.285299999999999</v>
+        <v>19.0992</v>
       </c>
       <c r="C4">
-        <v>91500</v>
+        <v>77500</v>
       </c>
       <c r="D4">
-        <v>50.89</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
@@ -475,13 +475,13 @@
         <v>515880</v>
       </c>
       <c r="B5">
-        <v>1.8378000000000001</v>
+        <v>0.91890000000000005</v>
       </c>
       <c r="C5">
-        <v>87500</v>
+        <v>175000</v>
       </c>
       <c r="D5">
-        <v>5.62</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
@@ -495,7 +495,7 @@
         <v>300</v>
       </c>
       <c r="D6">
-        <v>3.74</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
@@ -503,13 +503,13 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.1523000000000001</v>
+        <v>1.1631899999999999</v>
       </c>
       <c r="C7">
-        <v>42300</v>
+        <v>78600</v>
       </c>
       <c r="D7">
-        <v>1.94</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
@@ -517,13 +517,13 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1.5640000000000001</v>
+        <v>1.6318999999999999</v>
       </c>
       <c r="C8">
-        <v>42600</v>
+        <v>67200</v>
       </c>
       <c r="D8">
-        <v>3.05</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
@@ -531,13 +531,13 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>15.4</v>
+        <v>15.38</v>
       </c>
       <c r="C9">
-        <v>10000</v>
+        <v>9500</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.15">
@@ -545,13 +545,13 @@
         <v>688507</v>
       </c>
       <c r="B10">
-        <v>240</v>
+        <v>242.86670000000001</v>
       </c>
       <c r="C10">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>2.57</v>
       </c>
     </row>
   </sheetData>
